--- a/paper/Tables/prediction_cases_pooled.xlsx
+++ b/paper/Tables/prediction_cases_pooled.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joyce\Dropbox\Documentos_\Joyce_Seira\Pilot1\information_sett\paper\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isaac\Dropbox\ReplicationFinal\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF730D7-3AE5-4D20-9490-925DA6AFE91B}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EE304E-6883-4441-9E17-47265CF06946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{1DDB7879-9F24-4C6B-9F25-EBE6FFA84E93}"/>
+    <workbookView xWindow="-28920" yWindow="-8190" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prediction_cases_pooled" sheetId="1" r:id="rId1"/>
+    <sheet name="prediction_cases_pooled_panels" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +28,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,9 +38,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Observations</t>
+  </si>
+  <si>
+    <t>Constant (employee $\alpha$)</t>
+  </si>
+  <si>
+    <t>Employee's Lawyer ($\beta_1$)</t>
+  </si>
+  <si>
+    <t>Firm's Lawyer ($\beta_2$)</t>
   </si>
   <si>
     <t>File Fixed Effects</t>
@@ -57,21 +70,41 @@
     <t>Expectation</t>
   </si>
   <si>
-    <t>Employee's Lawyer</t>
+    <t>Panel A</t>
   </si>
   <si>
-    <t>Firm's Lawyer</t>
+    <t>Panel B</t>
   </si>
   <si>
-    <t>Constant</t>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Mid prediction</t>
+  </si>
+  <si>
+    <t>Max prediction</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Standar deviation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -87,7 +120,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -124,11 +157,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -146,6 +210,35 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -192,16 +285,16 @@
         </row>
         <row r="8">
           <cell r="B8" t="str">
-            <v>4.52</v>
+            <v>0.070</v>
           </cell>
           <cell r="C8" t="str">
-            <v>5902.2</v>
+            <v>11410.9</v>
           </cell>
           <cell r="D8" t="str">
-            <v>0.22</v>
+            <v>0.28</v>
           </cell>
           <cell r="E8" t="str">
-            <v>-0.097</v>
+            <v>-0.17</v>
           </cell>
         </row>
         <row r="9">
@@ -209,30 +302,30 @@
             <v/>
           </cell>
           <cell r="B9" t="str">
-            <v>(3.46)</v>
+            <v>(0.044)</v>
           </cell>
           <cell r="C9" t="str">
-            <v>(12555.8)</v>
+            <v>(13314.9)</v>
           </cell>
           <cell r="D9" t="str">
-            <v>(0.14)</v>
+            <v>(0.18)</v>
           </cell>
           <cell r="E9" t="str">
-            <v>(0.53)</v>
+            <v>(0.71)</v>
           </cell>
         </row>
         <row r="11">
           <cell r="B11" t="str">
-            <v>-27.4***</v>
+            <v>-0.25***</v>
           </cell>
           <cell r="C11" t="str">
-            <v>-27573.0**</v>
+            <v>-21804.2*</v>
           </cell>
           <cell r="D11" t="str">
-            <v>-0.96***</v>
+            <v>-0.86***</v>
           </cell>
           <cell r="E11" t="str">
-            <v>-0.38</v>
+            <v>-0.51</v>
           </cell>
         </row>
         <row r="12">
@@ -240,30 +333,30 @@
             <v/>
           </cell>
           <cell r="B12" t="str">
-            <v>(3.34)</v>
+            <v>(0.042)</v>
           </cell>
           <cell r="C12" t="str">
-            <v>(12083.0)</v>
+            <v>(12614.9)</v>
           </cell>
           <cell r="D12" t="str">
-            <v>(0.13)</v>
+            <v>(0.17)</v>
           </cell>
           <cell r="E12" t="str">
-            <v>(0.50)</v>
+            <v>(0.67)</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>75.0***</v>
+            <v>0.74***</v>
           </cell>
           <cell r="C14" t="str">
-            <v>74788.7***</v>
+            <v>66755.3***</v>
           </cell>
           <cell r="D14" t="str">
-            <v>1.64***</v>
+            <v>1.70***</v>
           </cell>
           <cell r="E14" t="str">
-            <v>0.73*</v>
+            <v>1.00*</v>
           </cell>
         </row>
         <row r="15">
@@ -271,30 +364,30 @@
             <v/>
           </cell>
           <cell r="B15" t="str">
-            <v>(2.86)</v>
+            <v>(0.036)</v>
           </cell>
           <cell r="C15" t="str">
-            <v>(10219.5)</v>
+            <v>(10791.5)</v>
           </cell>
           <cell r="D15" t="str">
-            <v>(0.11)</v>
+            <v>(0.15)</v>
           </cell>
           <cell r="E15" t="str">
-            <v>(0.43)</v>
+            <v>(0.58)</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>2214</v>
+            <v>1274</v>
           </cell>
           <cell r="C17" t="str">
-            <v>1859</v>
+            <v>1104</v>
           </cell>
           <cell r="D17" t="str">
-            <v>1952</v>
+            <v>1177</v>
           </cell>
           <cell r="E17" t="str">
-            <v>1632</v>
+            <v>1032</v>
           </cell>
         </row>
         <row r="18">
@@ -302,10 +395,10 @@
             <v>R-squared</v>
           </cell>
           <cell r="B18" t="str">
-            <v>0.83</v>
+            <v>0.79</v>
           </cell>
           <cell r="C18" t="str">
-            <v>0.89</v>
+            <v>0.91</v>
           </cell>
           <cell r="D18" t="str">
             <v>0.96</v>
@@ -319,16 +412,16 @@
             <v>p-value:Emp Law</v>
           </cell>
           <cell r="B19" t="str">
-            <v>2.1e-260</v>
+            <v>7.4e-161</v>
           </cell>
           <cell r="C19" t="str">
-            <v>3.3e-58</v>
+            <v>3.8e-43</v>
           </cell>
           <cell r="D19" t="str">
-            <v>6.9e-156</v>
+            <v>6.6e-99</v>
           </cell>
           <cell r="E19" t="str">
-            <v>0.00024</v>
+            <v>0.00089</v>
           </cell>
         </row>
         <row r="20">
@@ -336,16 +429,134 @@
             <v>p-value:Firm Law</v>
           </cell>
           <cell r="B20" t="str">
-            <v>2.7e-148</v>
+            <v>8.5e-111</v>
           </cell>
           <cell r="C20" t="str">
-            <v>9.6e-22</v>
+            <v>3.7e-21</v>
           </cell>
           <cell r="D20" t="str">
-            <v>3.8e-35</v>
+            <v>4.0e-37</v>
           </cell>
           <cell r="E20" t="str">
-            <v>0.070</v>
+            <v>0.036</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>(1)</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>(2)</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>(3)</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>(4)</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>0.885***</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>58,077***</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>1.713***</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>1.315***</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>(0.00288)</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>(1,794)</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>(0.0729)</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>(0.0619)</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v/>
+          </cell>
+          <cell r="C7" t="str">
+            <v/>
+          </cell>
+          <cell r="D7" t="str">
+            <v/>
+          </cell>
+          <cell r="E7" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>3,330</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>1,723</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>1,723</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>1,723</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>Ignores prob. (%)</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>13.08</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v/>
+          </cell>
+          <cell r="D10" t="str">
+            <v/>
+          </cell>
+          <cell r="E10" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>Standard deviation</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>0.166</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>74471</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>3.026</v>
+          </cell>
+          <cell r="E11" t="str">
+            <v>2.570</v>
           </cell>
         </row>
       </sheetData>
@@ -355,7 +566,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -650,39 +861,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E84D4E-CF42-42B1-A003-BD4DC1FD0253}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2"/>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="15"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="str">
         <f>[1]prediction_cases_pooled!A2</f>
         <v/>
@@ -704,191 +915,191 @@
         <v>(4)</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="str">
         <f>[1]prediction_cases_pooled!B8</f>
-        <v>4.52</v>
+        <v>0.070</v>
       </c>
       <c r="C5" s="1" t="str">
         <f>[1]prediction_cases_pooled!C8</f>
-        <v>5902.2</v>
+        <v>11410.9</v>
       </c>
       <c r="D5" s="1" t="str">
         <f>[1]prediction_cases_pooled!D8</f>
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>[1]prediction_cases_pooled!E8</f>
-        <v>-0.097</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>[1]prediction_cases_pooled!A9</f>
         <v/>
       </c>
       <c r="B6" s="1" t="str">
         <f>[1]prediction_cases_pooled!B9</f>
-        <v>(3.46)</v>
+        <v>(0.044)</v>
       </c>
       <c r="C6" s="1" t="str">
         <f>[1]prediction_cases_pooled!C9</f>
-        <v>(12555.8)</v>
+        <v>(13314.9)</v>
       </c>
       <c r="D6" s="1" t="str">
         <f>[1]prediction_cases_pooled!D9</f>
-        <v>(0.14)</v>
+        <v>(0.18)</v>
       </c>
       <c r="E6" s="1" t="str">
         <f>[1]prediction_cases_pooled!E9</f>
-        <v>(0.53)</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>(0.71)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1" t="str">
         <f>[1]prediction_cases_pooled!B11</f>
-        <v>-27.4***</v>
+        <v>-0.25***</v>
       </c>
       <c r="C7" s="1" t="str">
         <f>[1]prediction_cases_pooled!C11</f>
-        <v>-27573.0**</v>
+        <v>-21804.2*</v>
       </c>
       <c r="D7" s="1" t="str">
         <f>[1]prediction_cases_pooled!D11</f>
-        <v>-0.96***</v>
+        <v>-0.86***</v>
       </c>
       <c r="E7" s="1" t="str">
         <f>[1]prediction_cases_pooled!E11</f>
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>[1]prediction_cases_pooled!A12</f>
         <v/>
       </c>
       <c r="B8" s="1" t="str">
         <f>[1]prediction_cases_pooled!B12</f>
-        <v>(3.34)</v>
+        <v>(0.042)</v>
       </c>
       <c r="C8" s="1" t="str">
         <f>[1]prediction_cases_pooled!C12</f>
-        <v>(12083.0)</v>
+        <v>(12614.9)</v>
       </c>
       <c r="D8" s="1" t="str">
         <f>[1]prediction_cases_pooled!D12</f>
-        <v>(0.13)</v>
+        <v>(0.17)</v>
       </c>
       <c r="E8" s="1" t="str">
         <f>[1]prediction_cases_pooled!E12</f>
-        <v>(0.50)</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>(0.67)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="str">
         <f>[1]prediction_cases_pooled!B14</f>
-        <v>75.0***</v>
+        <v>0.74***</v>
       </c>
       <c r="C9" s="1" t="str">
         <f>[1]prediction_cases_pooled!C14</f>
-        <v>74788.7***</v>
+        <v>66755.3***</v>
       </c>
       <c r="D9" s="1" t="str">
         <f>[1]prediction_cases_pooled!D14</f>
-        <v>1.64***</v>
+        <v>1.70***</v>
       </c>
       <c r="E9" s="1" t="str">
         <f>[1]prediction_cases_pooled!E14</f>
-        <v>0.73*</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.00*</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>[1]prediction_cases_pooled!A15</f>
         <v/>
       </c>
       <c r="B10" s="1" t="str">
         <f>[1]prediction_cases_pooled!B15</f>
-        <v>(2.86)</v>
+        <v>(0.036)</v>
       </c>
       <c r="C10" s="1" t="str">
         <f>[1]prediction_cases_pooled!C15</f>
-        <v>(10219.5)</v>
+        <v>(10791.5)</v>
       </c>
       <c r="D10" s="1" t="str">
         <f>[1]prediction_cases_pooled!D15</f>
-        <v>(0.11)</v>
+        <v>(0.15)</v>
       </c>
       <c r="E10" s="1" t="str">
         <f>[1]prediction_cases_pooled!E15</f>
-        <v>(0.43)</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>(0.58)</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="7" t="str">
         <f>[1]prediction_cases_pooled!B17</f>
-        <v>2214</v>
+        <v>1274</v>
       </c>
       <c r="C12" s="7" t="str">
         <f>[1]prediction_cases_pooled!C17</f>
-        <v>1859</v>
+        <v>1104</v>
       </c>
       <c r="D12" s="7" t="str">
         <f>[1]prediction_cases_pooled!D17</f>
-        <v>1952</v>
+        <v>1177</v>
       </c>
       <c r="E12" s="7" t="str">
         <f>[1]prediction_cases_pooled!E17</f>
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>[1]prediction_cases_pooled!A18</f>
         <v>R-squared</v>
       </c>
       <c r="B14" s="1" t="str">
         <f>[1]prediction_cases_pooled!B18</f>
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="C14" s="1" t="str">
         <f>[1]prediction_cases_pooled!C18</f>
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="D14" s="1" t="str">
         <f>[1]prediction_cases_pooled!D18</f>
@@ -899,7 +1110,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>[1]prediction_cases_pooled!A19</f>
         <v>p-value:Emp Law</v>
@@ -921,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="str">
         <f>[1]prediction_cases_pooled!A20</f>
         <v>p-value:Firm Law</v>
@@ -940,10 +1151,10 @@
       </c>
       <c r="E16" s="5">
         <f>ROUND([1]prediction_cases_pooled!E20,1)</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:C2"/>
@@ -951,4 +1162,574 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A3:F32"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.90625" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="9"/>
+      <c r="B4" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="str">
+        <f>[1]prediction_cases_pooled!A2</f>
+        <v/>
+      </c>
+      <c r="B6" s="8" t="str">
+        <f>[1]prediction_cases_pooled!B2</f>
+        <v>(1)</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <f>[1]prediction_cases_pooled!C2</f>
+        <v>(2)</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="8" t="str">
+        <f>[1]prediction_cases_pooled!D2</f>
+        <v>(3)</v>
+      </c>
+      <c r="F6" s="8" t="str">
+        <f>[1]prediction_cases_pooled!E2</f>
+        <v>(4)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>[1]prediction_cases_pooled!B8</f>
+        <v>0.070</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>[1]prediction_cases_pooled!C8</f>
+        <v>11410.9</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="str">
+        <f>[1]prediction_cases_pooled!D8</f>
+        <v>0.28</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>[1]prediction_cases_pooled!E8</f>
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="str">
+        <f>[1]prediction_cases_pooled!A9</f>
+        <v/>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>[1]prediction_cases_pooled!B9</f>
+        <v>(0.044)</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f>[1]prediction_cases_pooled!C9</f>
+        <v>(13314.9)</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="str">
+        <f>[1]prediction_cases_pooled!D9</f>
+        <v>(0.18)</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f>[1]prediction_cases_pooled!E9</f>
+        <v>(0.71)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>[1]prediction_cases_pooled!B11</f>
+        <v>-0.25***</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f>[1]prediction_cases_pooled!C11</f>
+        <v>-21804.2*</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="str">
+        <f>[1]prediction_cases_pooled!D11</f>
+        <v>-0.86***</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f>[1]prediction_cases_pooled!E11</f>
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="str">
+        <f>[1]prediction_cases_pooled!A12</f>
+        <v/>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>[1]prediction_cases_pooled!B12</f>
+        <v>(0.042)</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>[1]prediction_cases_pooled!C12</f>
+        <v>(12614.9)</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="str">
+        <f>[1]prediction_cases_pooled!D12</f>
+        <v>(0.17)</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f>[1]prediction_cases_pooled!E12</f>
+        <v>(0.67)</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>[1]prediction_cases_pooled!B14</f>
+        <v>0.74***</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>[1]prediction_cases_pooled!C14</f>
+        <v>66755.3***</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="str">
+        <f>[1]prediction_cases_pooled!D14</f>
+        <v>1.70***</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f>[1]prediction_cases_pooled!E14</f>
+        <v>1.00*</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="str">
+        <f>[1]prediction_cases_pooled!A15</f>
+        <v/>
+      </c>
+      <c r="B12" s="1" t="str">
+        <f>[1]prediction_cases_pooled!B15</f>
+        <v>(0.036)</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f>[1]prediction_cases_pooled!C15</f>
+        <v>(10791.5)</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="str">
+        <f>[1]prediction_cases_pooled!D15</f>
+        <v>(0.15)</v>
+      </c>
+      <c r="F12" s="1" t="str">
+        <f>[1]prediction_cases_pooled!E15</f>
+        <v>(0.58)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <f>[1]prediction_cases_pooled!B17</f>
+        <v>1274</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <f>[1]prediction_cases_pooled!C17</f>
+        <v>1104</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="7" t="str">
+        <f>[1]prediction_cases_pooled!D17</f>
+        <v>1177</v>
+      </c>
+      <c r="F14" s="7" t="str">
+        <f>[1]prediction_cases_pooled!E17</f>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="str">
+        <f>[1]prediction_cases_pooled!A18</f>
+        <v>R-squared</v>
+      </c>
+      <c r="B16" s="1">
+        <f>ROUND([1]prediction_cases_pooled!B18,2)</f>
+        <v>0.79</v>
+      </c>
+      <c r="C16" s="1">
+        <f>ROUND([1]prediction_cases_pooled!C18,2)</f>
+        <v>0.91</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1">
+        <f>ROUND([1]prediction_cases_pooled!D18,2)</f>
+        <v>0.96</v>
+      </c>
+      <c r="F16" s="1">
+        <f>ROUND([1]prediction_cases_pooled!E18,2)</f>
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="str">
+        <f>[1]prediction_cases_pooled!A19</f>
+        <v>p-value:Emp Law</v>
+      </c>
+      <c r="B17" s="1">
+        <f>ROUND([1]prediction_cases_pooled!B19,2)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <f>ROUND([1]prediction_cases_pooled!C19,2)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1">
+        <f>ROUND([1]prediction_cases_pooled!D19,2)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <f>ROUND([1]prediction_cases_pooled!E19,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="str">
+        <f>[1]prediction_cases_pooled!A20</f>
+        <v>p-value:Firm Law</v>
+      </c>
+      <c r="B18" s="5">
+        <f>ROUND([1]prediction_cases_pooled!B20,2)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="5">
+        <f>ROUND([1]prediction_cases_pooled!C20,2)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5">
+        <f>ROUND([1]prediction_cases_pooled!D20,2)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <f>ROUND([1]prediction_cases_pooled!E20,2)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="9"/>
+      <c r="B21" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="19"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="16"/>
+    </row>
+    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="2"/>
+      <c r="B23" s="13" t="str">
+        <f>[2]Sheet1!B2</f>
+        <v>(1)</v>
+      </c>
+      <c r="C23" s="13" t="str">
+        <f>[2]Sheet1!C2</f>
+        <v>(2)</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13" t="str">
+        <f>[2]Sheet1!D2</f>
+        <v>(3)</v>
+      </c>
+      <c r="F23" s="13" t="str">
+        <f>[2]Sheet1!E2</f>
+        <v>(4)</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="10" t="str">
+        <f>[2]Sheet1!B5</f>
+        <v>0.885***</v>
+      </c>
+      <c r="C24" s="10" t="str">
+        <f>[2]Sheet1!C5</f>
+        <v>58,077***</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10" t="str">
+        <f>[2]Sheet1!D5</f>
+        <v>1.713***</v>
+      </c>
+      <c r="F24" s="10" t="str">
+        <f>[2]Sheet1!E5</f>
+        <v>1.315***</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10" t="str">
+        <f>[2]Sheet1!B6</f>
+        <v>(0.00288)</v>
+      </c>
+      <c r="C25" s="10" t="str">
+        <f>[2]Sheet1!C6</f>
+        <v>(1,794)</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10" t="str">
+        <f>[2]Sheet1!D6</f>
+        <v>(0.0729)</v>
+      </c>
+      <c r="F25" s="10" t="str">
+        <f>[2]Sheet1!E6</f>
+        <v>(0.0619)</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="10" t="str">
+        <f>[2]Sheet1!B11</f>
+        <v>0.166</v>
+      </c>
+      <c r="C26" s="10" t="str">
+        <f>[2]Sheet1!C11</f>
+        <v>74471</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10" t="str">
+        <f>[2]Sheet1!D11</f>
+        <v>3.026</v>
+      </c>
+      <c r="F26" s="10" t="str">
+        <f>[2]Sheet1!E11</f>
+        <v>2.570</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12" t="str">
+        <f>[2]Sheet1!B7</f>
+        <v/>
+      </c>
+      <c r="C27" s="12" t="str">
+        <f>[2]Sheet1!C7</f>
+        <v/>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12" t="str">
+        <f>[2]Sheet1!D7</f>
+        <v/>
+      </c>
+      <c r="F27" s="12" t="str">
+        <f>[2]Sheet1!E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="str">
+        <f>[2]Sheet1!B8</f>
+        <v>3,330</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <f>[2]Sheet1!C8</f>
+        <v>1,723</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="str">
+        <f>[2]Sheet1!D8</f>
+        <v>1,723</v>
+      </c>
+      <c r="F28" s="1" t="str">
+        <f>[2]Sheet1!E8</f>
+        <v>1,723</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="str">
+        <f>[2]Sheet1!A10</f>
+        <v>Ignores prob. (%)</v>
+      </c>
+      <c r="B29" s="1" t="str">
+        <f>[2]Sheet1!B10</f>
+        <v>13.08</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <f>[2]Sheet1!C10</f>
+        <v/>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="str">
+        <f>[2]Sheet1!D10</f>
+        <v/>
+      </c>
+      <c r="F29" s="1" t="str">
+        <f>[2]Sheet1!E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="str">
+        <f>[2]Sheet1!A11</f>
+        <v>Standard deviation</v>
+      </c>
+      <c r="B30" s="1" t="str">
+        <f>[2]Sheet1!B11</f>
+        <v>0.166</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <f>[2]Sheet1!C11</f>
+        <v>74471</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1" t="str">
+        <f>[2]Sheet1!D11</f>
+        <v>3.026</v>
+      </c>
+      <c r="F30" s="1" t="str">
+        <f>[2]Sheet1!E11</f>
+        <v>2.570</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="E21:F21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>